--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.89778905452574</v>
+        <v>5.995890721360433</v>
       </c>
       <c r="D2" t="n">
-        <v>37.43490461697396</v>
+        <v>6.083172000258268</v>
       </c>
       <c r="E2" t="n">
-        <v>11.03914452010101</v>
+        <v>1.793860984516415</v>
       </c>
       <c r="F2" t="n">
-        <v>11.02252138429192</v>
+        <v>1.791159724947437</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.61051172244571</v>
+        <v>5.786708154897427</v>
       </c>
       <c r="D3" t="n">
-        <v>36.95486485268956</v>
+        <v>6.005165538562053</v>
       </c>
       <c r="E3" t="n">
-        <v>11.03914452010101</v>
+        <v>1.793860984516415</v>
       </c>
       <c r="F3" t="n">
-        <v>11.02252138429192</v>
+        <v>1.791159724947437</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.3572502864851</v>
+        <v>3.63305317155383</v>
       </c>
       <c r="D4" t="n">
-        <v>22.59869874015913</v>
+        <v>3.672288545275858</v>
       </c>
       <c r="E4" t="n">
-        <v>11.03914452010101</v>
+        <v>1.793860984516415</v>
       </c>
       <c r="F4" t="n">
-        <v>11.02252138429192</v>
+        <v>1.791159724947437</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.38113109085721</v>
+        <v>4.936933802264297</v>
       </c>
       <c r="D5" t="n">
-        <v>30.13550852285051</v>
+        <v>4.897020134963207</v>
       </c>
       <c r="E5" t="n">
-        <v>11.03914452010101</v>
+        <v>1.793860984516415</v>
       </c>
       <c r="F5" t="n">
-        <v>11.02252138429192</v>
+        <v>1.791159724947437</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.48606410168136</v>
+        <v>3.166485416523221</v>
       </c>
       <c r="D6" t="n">
-        <v>18.48720222385072</v>
+        <v>3.004170361375742</v>
       </c>
       <c r="E6" t="n">
-        <v>11.03914452010101</v>
+        <v>1.793860984516415</v>
       </c>
       <c r="F6" t="n">
-        <v>11.02252138429192</v>
+        <v>1.791159724947437</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.55295138252265</v>
+        <v>3.33985459965993</v>
       </c>
       <c r="D7" t="n">
-        <v>20.69139758520396</v>
+        <v>3.362352107595644</v>
       </c>
       <c r="E7" t="n">
-        <v>11.03914452010101</v>
+        <v>1.793860984516415</v>
       </c>
       <c r="F7" t="n">
-        <v>11.02252138429192</v>
+        <v>1.791159724947437</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.732352910392</v>
+        <v>5.319007347938701</v>
       </c>
       <c r="D8" t="n">
-        <v>32.92919876163594</v>
+        <v>5.350994798765841</v>
       </c>
       <c r="E8" t="n">
-        <v>11.03914452010101</v>
+        <v>1.793860984516415</v>
       </c>
       <c r="F8" t="n">
-        <v>11.02252138429192</v>
+        <v>1.791159724947437</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.36889994810473</v>
+        <v>4.60994624156702</v>
       </c>
       <c r="D9" t="n">
-        <v>27.38423669222953</v>
+        <v>4.4499384624873</v>
       </c>
       <c r="E9" t="n">
-        <v>11.03914452010101</v>
+        <v>1.793860984516415</v>
       </c>
       <c r="F9" t="n">
-        <v>11.02252138429192</v>
+        <v>1.791159724947437</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.22205777185447</v>
+        <v>5.561084387926351</v>
       </c>
       <c r="D10" t="n">
-        <v>32.75819783962303</v>
+        <v>5.323207148938742</v>
       </c>
       <c r="E10" t="n">
-        <v>11.03914452010101</v>
+        <v>1.793860984516415</v>
       </c>
       <c r="F10" t="n">
-        <v>11.02252138429192</v>
+        <v>1.791159724947437</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>1.49943101924492</v>
+        <v>0.2436575406272995</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5182478059371287</v>
+        <v>0.08421526846478342</v>
       </c>
       <c r="E11" t="n">
-        <v>11.03914452010101</v>
+        <v>1.793860984516415</v>
       </c>
       <c r="F11" t="n">
-        <v>11.02252138429192</v>
+        <v>1.791159724947437</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>11.22965854307725</v>
+        <v>1.824819513250054</v>
       </c>
       <c r="D12" t="n">
-        <v>14.51113993084623</v>
+        <v>2.358060238762512</v>
       </c>
       <c r="E12" t="n">
-        <v>11.03914452010101</v>
+        <v>1.793860984516415</v>
       </c>
       <c r="F12" t="n">
-        <v>11.02252138429192</v>
+        <v>1.791159724947437</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.207759399389348</v>
+        <v>1.496260902400769</v>
       </c>
       <c r="D13" t="n">
-        <v>9.133265876391137</v>
+        <v>1.48415570491356</v>
       </c>
       <c r="E13" t="n">
-        <v>11.03914452010101</v>
+        <v>1.793860984516415</v>
       </c>
       <c r="F13" t="n">
-        <v>11.02252138429192</v>
+        <v>1.791159724947437</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
